--- a/data/trans_camb/IP26C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 0,01</t>
+          <t>-13,92; 0,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 3,75</t>
+          <t>-10,55; 3,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 2,13</t>
+          <t>-12,33; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 6,77</t>
+          <t>-8,12; 6,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 5,26</t>
+          <t>-8,14; 5,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 11,15</t>
+          <t>-4,39; 10,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 1,23</t>
+          <t>-8,18; 1,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 2,53</t>
+          <t>-7,66; 2,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 4,79</t>
+          <t>-5,02; 5,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,83; 15,23</t>
+          <t>-79,54; 8,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,5; 49,25</t>
+          <t>-64,89; 47,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,38; 25,67</t>
+          <t>-70,5; 17,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 96,78</t>
+          <t>-57,92; 100,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 86,12</t>
+          <t>-60,02; 90,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 156,12</t>
+          <t>-31,41; 172,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,45; 15,29</t>
+          <t>-57,95; 22,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 31,18</t>
+          <t>-53,61; 23,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 55,49</t>
+          <t>-35,69; 61,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 11,96</t>
+          <t>-3,82; 11,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 6,17</t>
+          <t>-7,12; 6,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 7,84</t>
+          <t>-7,02; 7,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 10,44</t>
+          <t>-2,04; 11,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 7,57</t>
+          <t>-4,0; 8,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 10,17</t>
+          <t>-2,91; 10,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 9,59</t>
+          <t>-0,18; 9,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 5,42</t>
+          <t>-3,43; 5,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 6,7</t>
+          <t>-2,98; 6,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 196,27</t>
+          <t>-31,59; 203,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 117,19</t>
+          <t>-54,08; 107,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,68; 137,95</t>
+          <t>-55,19; 136,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 314,97</t>
+          <t>-26,97; 375,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,3; 221,86</t>
+          <t>-46,69; 251,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 310,46</t>
+          <t>-38,46; 320,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 176,94</t>
+          <t>-2,9; 184,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 100,37</t>
+          <t>-33,83; 103,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 129,46</t>
+          <t>-31,31; 117,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 5,85</t>
+          <t>-10,97; 5,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 3,98</t>
+          <t>-12,66; 4,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 5,57</t>
+          <t>-13,49; 4,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 2,74</t>
+          <t>-10,92; 3,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 5,99</t>
+          <t>-10,42; 6,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 14,74</t>
+          <t>-5,39; 13,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 1,79</t>
+          <t>-9,51; 1,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 2,9</t>
+          <t>-9,27; 2,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 6,67</t>
+          <t>-7,76; 6,12</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 75,23</t>
+          <t>-60,44; 80,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 50,07</t>
+          <t>-72,3; 71,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,46; 85,23</t>
+          <t>-79,0; 54,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 30,15</t>
+          <t>-64,88; 36,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 60,31</t>
+          <t>-58,56; 65,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,99; 142,47</t>
+          <t>-35,9; 132,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 17,31</t>
+          <t>-55,19; 19,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 29,88</t>
+          <t>-55,66; 28,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 63,08</t>
+          <t>-47,3; 56,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 3,03</t>
+          <t>-6,27; 2,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 5,56</t>
+          <t>-4,2; 5,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 2,52</t>
+          <t>-6,31; 3,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 2,88</t>
+          <t>-7,01; 2,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,08</t>
+          <t>-7,63; 2,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -0,93</t>
+          <t>-9,83; -0,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 1,55</t>
+          <t>-5,26; 1,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,24</t>
+          <t>-3,99; 2,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -0,15</t>
+          <t>-6,9; -0,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 46,17</t>
+          <t>-54,77; 39,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 76,4</t>
+          <t>-37,71; 71,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 35,91</t>
+          <t>-54,56; 40,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 31,11</t>
+          <t>-47,53; 26,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 22,78</t>
+          <t>-51,04; 23,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,36; -8,23</t>
+          <t>-68,06; -6,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 17,69</t>
+          <t>-41,91; 15,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 24,51</t>
+          <t>-32,48; 28,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,39; 2,35</t>
+          <t>-55,05; -2,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 5,59</t>
+          <t>-8,17; 5,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 0,66</t>
+          <t>-12,22; 0,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 8,32</t>
+          <t>-5,76; 8,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 13,34</t>
+          <t>1,89; 13,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 9,12</t>
+          <t>-1,06; 8,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 10,87</t>
+          <t>-0,32; 10,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 7,93</t>
+          <t>-0,61; 8,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 4,02</t>
+          <t>-4,63; 3,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 7,99</t>
+          <t>-1,15; 7,76</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,05; 70,68</t>
+          <t>-50,76; 63,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-70,81; 14,49</t>
+          <t>-71,91; 12,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 105,98</t>
+          <t>-37,41; 108,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25,87; 466,11</t>
+          <t>17,49; 453,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 324,95</t>
+          <t>-20,13; 295,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 374,23</t>
+          <t>-14,07; 344,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 133,46</t>
+          <t>-7,75; 144,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 72,3</t>
+          <t>-42,28; 55,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 130,95</t>
+          <t>-12,69; 126,24</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 13,87</t>
+          <t>-8,22; 13,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 4,55</t>
+          <t>-14,2; 4,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-19,36; -3,04</t>
+          <t>-20,03; -4,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,34; 19,11</t>
+          <t>2,72; 19,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 8,4</t>
+          <t>-6,03; 8,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,32; 22,94</t>
+          <t>3,31; 24,58</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 12,81</t>
+          <t>-0,59; 13,35</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 3,43</t>
+          <t>-8,68; 3,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 7,98</t>
+          <t>-6,22; 7,26</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-41,4; 140,29</t>
+          <t>-44,17; 119,3</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-71,87; 48,02</t>
+          <t>-69,7; 41,26</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-88,2; -22,17</t>
+          <t>-90,08; -27,46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8,98; 551,36</t>
+          <t>18,48; 650,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-64,75; 280,88</t>
+          <t>-68,52; 265,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,67; 653,47</t>
+          <t>16,35; 710,49</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 143,21</t>
+          <t>-5,86; 154,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-61,66; 40,04</t>
+          <t>-60,31; 44,32</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 99,56</t>
+          <t>-42,11; 86,39</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,31</t>
+          <t>-4,31; 1,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,36</t>
+          <t>-4,95; 0,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -0,07</t>
+          <t>-5,67; 0,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,4</t>
+          <t>-0,81; 4,64</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,19</t>
+          <t>-2,9; 2,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,51</t>
+          <t>-0,98; 4,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,35</t>
+          <t>-1,65; 2,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,49</t>
+          <t>-3,25; 0,56</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,6</t>
+          <t>-2,54; 1,43</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 12,81</t>
+          <t>-32,89; 15,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 5,56</t>
+          <t>-38,25; 5,56</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 0,39</t>
+          <t>-42,05; 4,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 54,42</t>
+          <t>-7,62; 57,47</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 26,71</t>
+          <t>-26,78; 27,26</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 56,46</t>
+          <t>-9,61; 53,24</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 24,42</t>
+          <t>-14,33; 24,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 5,38</t>
+          <t>-28,09; 6,01</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 16,37</t>
+          <t>-22,17; 15,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 0,31</t>
+          <t>-13,45; 0,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 3,83</t>
+          <t>-10,81; 3,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 1,35</t>
+          <t>-11,89; 2,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 6,28</t>
+          <t>-7,58; 5,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 5,75</t>
+          <t>-8,52; 4,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 10,77</t>
+          <t>-3,47; 10,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,76</t>
+          <t>-8,68; 1,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 2,03</t>
+          <t>-7,94; 2,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,52</t>
+          <t>-5,53; 4,84</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,54; 8,03</t>
+          <t>-79,44; 12,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,89; 47,12</t>
+          <t>-66,56; 48,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,5; 17,64</t>
+          <t>-71,17; 28,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,92; 100,07</t>
+          <t>-57,24; 88,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 90,35</t>
+          <t>-61,37; 71,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 172,55</t>
+          <t>-28,17; 164,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 22,47</t>
+          <t>-60,08; 14,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,61; 23,06</t>
+          <t>-53,65; 23,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 61,15</t>
+          <t>-40,5; 53,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 11,96</t>
+          <t>-3,71; 11,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 6,14</t>
+          <t>-7,29; 6,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 7,84</t>
+          <t>-6,7; 7,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 11,78</t>
+          <t>-1,57; 11,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 8,29</t>
+          <t>-3,45; 8,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 10,5</t>
+          <t>-2,57; 9,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 9,36</t>
+          <t>-0,81; 9,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 5,79</t>
+          <t>-4,07; 5,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 6,58</t>
+          <t>-3,14; 6,88</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 203,76</t>
+          <t>-31,69; 195,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 107,87</t>
+          <t>-56,51; 126,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 136,98</t>
+          <t>-52,47; 123,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 375,74</t>
+          <t>-21,37; 306,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 251,4</t>
+          <t>-41,15; 288,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 320,09</t>
+          <t>-29,58; 310,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 184,62</t>
+          <t>-10,39; 171,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 103,65</t>
+          <t>-39,15; 97,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 117,9</t>
+          <t>-33,25; 128,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 5,72</t>
+          <t>-11,49; 4,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 4,72</t>
+          <t>-12,92; 4,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 4,16</t>
+          <t>-13,24; 5,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 3,51</t>
+          <t>-11,04; 4,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 6,48</t>
+          <t>-10,27; 7,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 13,86</t>
+          <t>-6,04; 12,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 1,57</t>
+          <t>-9,64; 2,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 2,82</t>
+          <t>-9,56; 2,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 6,12</t>
+          <t>-6,88; 6,9</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,44; 80,93</t>
+          <t>-65,24; 63,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,3; 71,03</t>
+          <t>-74,34; 63,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 54,32</t>
+          <t>-77,97; 79,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,88; 36,49</t>
+          <t>-64,94; 39,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,56; 65,54</t>
+          <t>-59,4; 73,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 132,53</t>
+          <t>-37,37; 123,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 19,58</t>
+          <t>-57,26; 21,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,66; 28,54</t>
+          <t>-57,01; 22,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 56,44</t>
+          <t>-44,97; 68,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 2,75</t>
+          <t>-6,46; 2,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 5,24</t>
+          <t>-3,77; 5,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 3,15</t>
+          <t>-6,39; 3,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 2,51</t>
+          <t>-7,25; 3,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,22</t>
+          <t>-6,91; 2,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,83; -0,82</t>
+          <t>-10,15; -0,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 1,39</t>
+          <t>-5,04; 1,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,57</t>
+          <t>-4,38; 2,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -0,22</t>
+          <t>-6,84; -0,25</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,77; 39,82</t>
+          <t>-53,45; 42,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 71,01</t>
+          <t>-32,97; 88,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,56; 40,96</t>
+          <t>-54,13; 43,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 26,43</t>
+          <t>-48,28; 32,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,04; 23,55</t>
+          <t>-46,86; 24,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,06; -6,93</t>
+          <t>-67,35; -4,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 15,35</t>
+          <t>-39,83; 18,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 28,68</t>
+          <t>-34,86; 25,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,05; -2,26</t>
+          <t>-53,26; -2,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,25</t>
+          <t>-8,3; 5,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 0,86</t>
+          <t>-11,32; 1,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 8,49</t>
+          <t>-6,32; 8,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 13,27</t>
+          <t>2,4; 13,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 8,32</t>
+          <t>-0,7; 8,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 10,43</t>
+          <t>0,02; 10,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 8,37</t>
+          <t>-0,79; 7,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 3,23</t>
+          <t>-4,77; 3,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 7,76</t>
+          <t>-1,22; 8,26</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 63,48</t>
+          <t>-51,98; 73,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 12,75</t>
+          <t>-67,01; 22,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 108,65</t>
+          <t>-39,8; 102,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,49; 453,96</t>
+          <t>20,19; 446,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 295,84</t>
+          <t>-14,85; 334,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 344,34</t>
+          <t>-12,61; 334,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 144,21</t>
+          <t>-7,64; 130,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,28; 55,37</t>
+          <t>-45,29; 56,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 126,24</t>
+          <t>-12,93; 142,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 13,97</t>
+          <t>-8,37; 13,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 4,38</t>
+          <t>-14,81; 4,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-20,03; -4,06</t>
+          <t>-18,95; -4,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,72; 19,62</t>
+          <t>2,54; 19,99</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 8,94</t>
+          <t>-6,87; 6,98</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,31; 24,58</t>
+          <t>2,3; 22,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 13,35</t>
+          <t>-0,33; 14,22</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 3,65</t>
+          <t>-8,42; 3,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 7,26</t>
+          <t>-6,0; 7,22</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 119,3</t>
+          <t>-43,2; 115,96</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-69,7; 41,26</t>
+          <t>-70,01; 37,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-90,08; -27,46</t>
+          <t>-88,6; -28,02</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18,48; 650,42</t>
+          <t>17,58; 646,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-68,52; 265,47</t>
+          <t>-73,55; 232,24</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,35; 710,49</t>
+          <t>10,03; 627,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 154,72</t>
+          <t>-7,63; 160,94</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-60,31; 44,32</t>
+          <t>-60,58; 39,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 86,39</t>
+          <t>-43,6; 84,46</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,5</t>
+          <t>-4,11; 1,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,52</t>
+          <t>-5,22; 0,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 0,42</t>
+          <t>-5,98; 0,05</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,64</t>
+          <t>-0,9; 4,48</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,21</t>
+          <t>-2,95; 2,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,4</t>
+          <t>-1,2; 4,26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,43</t>
+          <t>-1,69; 2,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,56</t>
+          <t>-3,37; 0,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,43</t>
+          <t>-2,36; 1,63</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 15,05</t>
+          <t>-30,99; 15,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 5,56</t>
+          <t>-39,12; 3,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 4,47</t>
+          <t>-44,63; 0,34</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 57,47</t>
+          <t>-8,64; 53,47</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 27,26</t>
+          <t>-26,94; 25,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 53,24</t>
+          <t>-11,96; 51,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 24,5</t>
+          <t>-14,79; 22,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 6,01</t>
+          <t>-29,13; 3,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 15,49</t>
+          <t>-20,57; 17,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,68</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-6,5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,55</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>-4,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 0,48</t>
+          <t>-7,17; 6,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 3,83</t>
+          <t>-8,56; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 2,51</t>
+          <t>-3,8; 11,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 5,99</t>
+          <t>-13,57; 0,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 4,68</t>
+          <t>-10,67; 3,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 10,49</t>
+          <t>-10,97; 2,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 1,23</t>
+          <t>-8,67; 1,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 2,04</t>
+          <t>-7,53; 2,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,84</t>
+          <t>-5,18; 5,23</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-6,22%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-17,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35,36%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-50,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-27,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-35,01%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,22%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-17,28%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>-32,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-3,07%</t>
+          <t>-0,51%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,44; 12,45</t>
+          <t>-53,54; 96,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-66,56; 48,67</t>
+          <t>-62,13; 86,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,17; 28,95</t>
+          <t>-29,02; 161,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,24; 88,07</t>
+          <t>-79,83; 15,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 71,39</t>
+          <t>-64,5; 49,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 164,16</t>
+          <t>-64,76; 33,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,08; 14,84</t>
+          <t>-59,45; 15,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,65; 23,33</t>
+          <t>-52,96; 31,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 53,33</t>
+          <t>-36,26; 62,48</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,21</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,94</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,25</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,18</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,34</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 11,45</t>
+          <t>-1,61; 10,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 6,66</t>
+          <t>-3,96; 7,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 7,32</t>
+          <t>-2,77; 11,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 11,25</t>
+          <t>-3,8; 11,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 8,49</t>
+          <t>-7,71; 6,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 9,88</t>
+          <t>-6,85; 7,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 9,55</t>
+          <t>-0,69; 9,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 5,36</t>
+          <t>-3,52; 5,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 6,88</t>
+          <t>-3,06; 7,06</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>73,84%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>63,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>44,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-2,58%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73,84%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,68%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 195,2</t>
+          <t>-27,06; 314,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,51; 126,51</t>
+          <t>-50,3; 221,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 123,76</t>
+          <t>-36,11; 357,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 306,75</t>
+          <t>-30,39; 196,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 288,42</t>
+          <t>-57,13; 117,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 310,72</t>
+          <t>-54,44; 135,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 171,01</t>
+          <t>-8,56; 176,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 97,01</t>
+          <t>-35,1; 100,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 128,91</t>
+          <t>-30,0; 139,44</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,09</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,52</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,04</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,53</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,8</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,09</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>-4,51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 4,98</t>
+          <t>-11,78; 2,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 4,83</t>
+          <t>-9,98; 5,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 5,37</t>
+          <t>-4,79; 17,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 4,15</t>
+          <t>-11,02; 5,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 7,01</t>
+          <t>-13,09; 3,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 12,98</t>
+          <t>-13,34; 6,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 2,14</t>
+          <t>-9,71; 1,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 2,4</t>
+          <t>-9,19; 2,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 6,9</t>
+          <t>-7,0; 7,32</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-27,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-15,12%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32,64%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-22,92%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-34,16%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-34,87%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-27,42%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-15,12%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>-34,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,33%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 63,55</t>
+          <t>-66,48; 30,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,34; 63,26</t>
+          <t>-58,83; 60,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,97; 79,33</t>
+          <t>-29,61; 161,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,94; 39,61</t>
+          <t>-62,91; 75,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,4; 73,55</t>
+          <t>-74,72; 50,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 123,1</t>
+          <t>-74,33; 88,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 21,97</t>
+          <t>-56,37; 17,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 22,9</t>
+          <t>-55,37; 29,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 68,75</t>
+          <t>-43,03; 67,7</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,08</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,54</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-5,11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,08</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,54</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,48</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-2,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 2,83</t>
+          <t>-7,0; 2,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 5,9</t>
+          <t>-7,64; 2,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 3,28</t>
+          <t>-9,96; -0,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 3,03</t>
+          <t>-6,28; 3,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 2,6</t>
+          <t>-3,81; 5,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -0,49</t>
+          <t>-5,15; 4,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,6</t>
+          <t>-5,25; 1,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 2,35</t>
+          <t>-4,09; 2,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -0,25</t>
+          <t>-6,02; 0,92</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-17,11%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-20,89%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-42,03%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-16,04%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>8,88%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-16,18%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-17,11%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-20,89%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,01%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-32,35%</t>
+          <t>-23,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 42,12</t>
+          <t>-48,39; 31,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 88,99</t>
+          <t>-52,89; 22,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 43,89</t>
+          <t>-67,99; -1,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,28; 32,34</t>
+          <t>-52,63; 46,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 24,64</t>
+          <t>-33,32; 76,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,35; -4,08</t>
+          <t>-43,2; 65,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 18,14</t>
+          <t>-41,46; 17,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 25,17</t>
+          <t>-32,61; 24,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,26; -2,29</t>
+          <t>-47,21; 11,17</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,67</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,81</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,04</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-5,0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,67</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,7</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 5,81</t>
+          <t>2,51; 13,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 1,26</t>
+          <t>-0,9; 9,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 8,52</t>
+          <t>-0,1; 12,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 13,11</t>
+          <t>-8,68; 5,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 8,67</t>
+          <t>-12,14; 0,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 10,82</t>
+          <t>-5,43; 9,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 7,76</t>
+          <t>-0,45; 7,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 3,31</t>
+          <t>-3,89; 4,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 8,26</t>
+          <t>-0,65; 8,95</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>161,89%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>78,09%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>122,66%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-8,52%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-40,76%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>161,89%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>78,09%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>106,54%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 73,64</t>
+          <t>25,87; 466,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-67,01; 22,39</t>
+          <t>-15,89; 324,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 102,66</t>
+          <t>-9,47; 410,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,19; 446,45</t>
+          <t>-51,05; 70,68</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 334,51</t>
+          <t>-70,81; 14,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 334,12</t>
+          <t>-38,35; 110,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 130,23</t>
+          <t>-5,22; 133,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,29; 56,94</t>
+          <t>-38,44; 72,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 142,56</t>
+          <t>-8,13; 147,94</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>10,49</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,37</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11,47</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-5,33</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-11,19</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10,49</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,36</t>
+          <t>-11,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>-0,25</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 13,34</t>
+          <t>2,34; 19,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 4,14</t>
+          <t>-5,72; 8,4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -4,06</t>
+          <t>2,66; 21,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,54; 19,99</t>
+          <t>-8,41; 13,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 6,98</t>
+          <t>-15,17; 4,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,3; 22,64</t>
+          <t>-19,4; -3,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 14,22</t>
+          <t>-1,08; 12,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 3,24</t>
+          <t>-8,42; 3,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 7,22</t>
+          <t>-6,07; 6,65</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>162,57%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>177,82%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>12,38%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-33,07%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-69,37%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>162,57%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>191,63%</t>
+          <t>-71,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>-2,24%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-43,2; 115,96</t>
+          <t>8,98; 551,36</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-70,01; 37,81</t>
+          <t>-64,75; 280,88</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-88,6; -28,02</t>
+          <t>12,03; 668,93</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17,58; 646,42</t>
+          <t>-41,4; 140,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-73,55; 232,24</t>
+          <t>-71,87; 48,02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,03; 627,12</t>
+          <t>-88,6; -26,14</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 160,94</t>
+          <t>-10,22; 143,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-60,58; 39,69</t>
+          <t>-61,66; 40,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 84,46</t>
+          <t>-42,94; 89,12</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2,04</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,32</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,36</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,7</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>-2,0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 1,55</t>
+          <t>-0,95; 4,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 0,34</t>
+          <t>-2,72; 2,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 0,05</t>
+          <t>-0,84; 5,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,48</t>
+          <t>-4,27; 1,31</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,06</t>
+          <t>-5,03; 0,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 4,26</t>
+          <t>-4,82; 0,75</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,19</t>
+          <t>-1,7; 2,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,34</t>
+          <t>-3,33; 0,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,63</t>
+          <t>-1,7; 2,12</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>19,77%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-4,54%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>21,62%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-11,32%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-20,22%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-23,1%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>19,77%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-4,54%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>-17,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-4,16%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,99; 15,44</t>
+          <t>-7,5; 54,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 3,95</t>
+          <t>-26,08; 26,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 0,34</t>
+          <t>-7,48; 63,4</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 53,47</t>
+          <t>-32,17; 12,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,94; 25,7</t>
+          <t>-38,12; 5,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 51,5</t>
+          <t>-36,38; 6,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 22,85</t>
+          <t>-14,7; 24,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 3,56</t>
+          <t>-29,12; 5,38</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 17,15</t>
+          <t>-15,09; 22,06</t>
         </is>
       </c>
     </row>
